--- a/outputs/marine_equipment/Сравнение_контейнеров.xlsx
+++ b/outputs/marine_equipment/Сравнение_контейнеров.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
